--- a/Team-Data/2014-15/1-28-2014-15.xlsx
+++ b/Team-Data/2014-15/1-28-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.826</v>
+        <v>0.822</v>
       </c>
       <c r="H2" t="n">
         <v>48.2</v>
@@ -688,19 +755,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N2" t="n">
         <v>0.387</v>
       </c>
       <c r="O2" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P2" t="n">
         <v>22.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="R2" t="n">
         <v>8.5</v>
@@ -709,16 +776,16 @@
         <v>32.5</v>
       </c>
       <c r="T2" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
         <v>26.2</v>
       </c>
       <c r="V2" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.6</v>
@@ -733,13 +800,13 @@
         <v>20.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.6</v>
+        <v>103.4</v>
       </c>
       <c r="AC2" t="n">
         <v>7.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -772,10 +839,10 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -787,13 +854,13 @@
         <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -802,7 +869,7 @@
         <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
         <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="H3" t="n">
         <v>48.6</v>
@@ -861,7 +928,7 @@
         <v>39.6</v>
       </c>
       <c r="J3" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.452</v>
@@ -876,25 +943,25 @@
         <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="P3" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="Q3" t="n">
         <v>0.756</v>
       </c>
       <c r="R3" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
         <v>32.7</v>
       </c>
       <c r="T3" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U3" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
@@ -906,19 +973,19 @@
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.8</v>
+        <v>101.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD3" t="n">
         <v>28</v>
@@ -927,7 +994,7 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>21</v>
@@ -945,7 +1012,7 @@
         <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
@@ -960,10 +1027,10 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
         <v>12</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -987,7 +1054,7 @@
         <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,7 +1110,7 @@
         <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.444</v>
@@ -1052,34 +1119,34 @@
         <v>6.6</v>
       </c>
       <c r="M4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="O4" t="n">
         <v>16.4</v>
       </c>
       <c r="P4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T4" t="n">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.3</v>
@@ -1088,31 +1155,31 @@
         <v>4.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1121,7 +1188,7 @@
         <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4" t="n">
         <v>20</v>
@@ -1130,19 +1197,19 @@
         <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1157,16 +1224,16 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
         <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.413</v>
+        <v>0.422</v>
       </c>
       <c r="H5" t="n">
         <v>48.8</v>
@@ -1237,28 +1304,28 @@
         <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P5" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="R5" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S5" t="n">
         <v>33.4</v>
       </c>
       <c r="T5" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V5" t="n">
         <v>11.7</v>
@@ -1276,16 +1343,16 @@
         <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1318,13 +1385,13 @@
         <v>29</v>
       </c>
       <c r="AO5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>20</v>
@@ -1333,7 +1400,7 @@
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>27</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>18</v>
@@ -1509,19 +1576,19 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
         <v>4</v>
       </c>
-      <c r="AS6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0.574</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1592,64 +1659,64 @@
         <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M7" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
         <v>18.7</v>
       </c>
       <c r="P7" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R7" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S7" t="n">
         <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y7" t="n">
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1664,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
@@ -1673,7 +1740,7 @@
         <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM7" t="n">
         <v>10</v>
@@ -1682,16 +1749,16 @@
         <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>24</v>
@@ -1700,16 +1767,16 @@
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
         <v>18</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1768,28 +1835,28 @@
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="J8" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L8" t="n">
         <v>9.4</v>
       </c>
       <c r="M8" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0.764</v>
@@ -1798,58 +1865,58 @@
         <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
         <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" t="n">
         <v>22</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.3</v>
+        <v>107.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" t="n">
         <v>8</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>9</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1864,37 +1931,37 @@
         <v>12</v>
       </c>
       <c r="AO8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP8" t="n">
         <v>19</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>20</v>
       </c>
       <c r="AQ8" t="n">
         <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT8" t="n">
         <v>21</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
       </c>
       <c r="AV8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1903,10 +1970,10 @@
         <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>0.413</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1962,34 +2029,34 @@
         <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.328</v>
+        <v>0.324</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.735</v>
       </c>
       <c r="R9" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="U9" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V9" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
@@ -2004,28 +2071,28 @@
         <v>23.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>101.6</v>
+        <v>101.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2037,19 +2104,19 @@
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>12</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2064,10 +2131,10 @@
         <v>5</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2076,19 +2143,19 @@
         <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -2117,85 +2184,85 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.362</v>
+        <v>0.37</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>36.6</v>
       </c>
       <c r="J10" t="n">
-        <v>85.8</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.423</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="O10" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P10" t="n">
         <v>23</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="R10" t="n">
         <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T10" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA10" t="n">
         <v>19.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,25 +2274,25 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM10" t="n">
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2246,7 +2313,7 @@
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2258,7 +2325,7 @@
         <v>19</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>7</v>
@@ -2267,10 +2334,10 @@
         <v>23</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2416,16 +2483,16 @@
         <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR11" t="n">
         <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -2496,40 +2563,40 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.44</v>
       </c>
       <c r="L12" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
         <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U12" t="n">
         <v>21.2</v>
@@ -2538,46 +2605,46 @@
         <v>17.4</v>
       </c>
       <c r="W12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.8</v>
+        <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
         <v>13</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2592,25 +2659,25 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
         <v>13</v>
       </c>
       <c r="AU12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,19 +2686,19 @@
         <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
@@ -2756,22 +2823,22 @@
         <v>17</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>23</v>
@@ -2801,13 +2868,13 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2816,7 +2883,7 @@
         <v>26</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.696</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.475</v>
@@ -2872,40 +2939,40 @@
         <v>10.1</v>
       </c>
       <c r="M14" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P14" t="n">
         <v>25.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R14" t="n">
         <v>9</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="V14" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W14" t="n">
         <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3</v>
@@ -2914,25 +2981,25 @@
         <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>107</v>
+        <v>107.3</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2941,10 +3008,10 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -2959,10 +3026,10 @@
         <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>27</v>
@@ -2977,13 +3044,13 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.261</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O15" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R15" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S15" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="U15" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V15" t="n">
         <v>13.1</v>
@@ -3090,22 +3157,22 @@
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
         <v>18</v>
       </c>
-      <c r="AI15" t="n">
-        <v>17</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK15" t="n">
         <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP15" t="n">
         <v>9</v>
       </c>
-      <c r="AP15" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
         <v>18</v>
@@ -3159,7 +3226,7 @@
         <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
         <v>18</v>
@@ -3168,13 +3235,13 @@
         <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA15" t="n">
         <v>18</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3323,10 +3390,10 @@
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
         <v>23</v>
@@ -3338,7 +3405,7 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
         <v>7</v>
@@ -3353,13 +3420,13 @@
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3499,10 +3566,10 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3520,10 +3587,10 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>9</v>
@@ -3532,13 +3599,13 @@
         <v>26</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3651,34 +3718,34 @@
         <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
         <v>8</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN18" t="n">
         <v>5</v>
@@ -3690,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
@@ -3711,13 +3778,13 @@
         <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.178</v>
+        <v>0.159</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J19" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>15.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O19" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.748</v>
+        <v>0.744</v>
       </c>
       <c r="R19" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="S19" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U19" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.6</v>
@@ -3821,19 +3888,19 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA19" t="n">
         <v>21.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.4</v>
+        <v>-9.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3866,13 +3933,13 @@
         <v>22</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3881,7 +3948,7 @@
         <v>30</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU19" t="n">
         <v>11</v>
@@ -3896,16 +3963,16 @@
         <v>24</v>
       </c>
       <c r="AY19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
         <v>7</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>29</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -3940,28 +4007,28 @@
         <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.511</v>
+        <v>0.533</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M20" t="n">
         <v>18.8</v>
@@ -3970,34 +4037,34 @@
         <v>0.343</v>
       </c>
       <c r="O20" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.755</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="U20" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>13.1</v>
       </c>
       <c r="W20" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4009,13 +4076,13 @@
         <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>100</v>
+        <v>100.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4027,16 +4094,16 @@
         <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,37 +4112,37 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP20" t="n">
         <v>17</v>
       </c>
-      <c r="AP20" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>17</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.196</v>
+        <v>0.178</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J21" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
@@ -4149,7 +4216,7 @@
         <v>20.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
         <v>13.6</v>
@@ -4158,46 +4225,46 @@
         <v>17.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R21" t="n">
         <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T21" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
         <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA21" t="n">
         <v>18.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-7.6</v>
+        <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
@@ -4209,10 +4276,10 @@
         <v>28</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ21" t="n">
         <v>22</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4248,19 +4315,19 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV21" t="n">
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
         <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J22" t="n">
         <v>85.2</v>
@@ -4325,34 +4392,34 @@
         <v>0.44</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
         <v>23</v>
       </c>
       <c r="N22" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="O22" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P22" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.742</v>
+        <v>0.74</v>
       </c>
       <c r="R22" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S22" t="n">
         <v>34.6</v>
       </c>
       <c r="T22" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="U22" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V22" t="n">
         <v>14.9</v>
@@ -4361,10 +4428,10 @@
         <v>7.3</v>
       </c>
       <c r="X22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
         <v>22.6</v>
@@ -4373,31 +4440,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
         <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK22" t="n">
         <v>22</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO22" t="n">
         <v>12</v>
@@ -4421,7 +4488,7 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4436,19 +4503,19 @@
         <v>22</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4550,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E23" t="n">
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.319</v>
+        <v>0.313</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.364</v>
       </c>
       <c r="O23" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="P23" t="n">
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI23" t="n">
         <v>16</v>
@@ -4582,10 +4649,10 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>23</v>
@@ -4600,7 +4667,7 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>28</v>
@@ -4615,16 +4682,16 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.196</v>
+        <v>0.178</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="J24" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="N24" t="n">
         <v>0.297</v>
       </c>
       <c r="O24" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="Q24" t="n">
         <v>0.681</v>
@@ -4710,40 +4777,40 @@
         <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U24" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V24" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="W24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y24" t="n">
         <v>5.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB24" t="n">
         <v>89.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.1</v>
+        <v>-12.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>10</v>
@@ -4785,16 +4852,16 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>27</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4809,7 +4876,7 @@
         <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -4847,19 +4914,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.574</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I25" t="n">
         <v>40.2</v>
@@ -4868,28 +4935,28 @@
         <v>86.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N25" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.789</v>
       </c>
       <c r="R25" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S25" t="n">
         <v>31.7</v>
@@ -4907,25 +4974,25 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
         <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.3</v>
+        <v>107.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4967,10 +5034,10 @@
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>18</v>
@@ -4985,22 +5052,22 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" t="n">
         <v>32</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>0.696</v>
+        <v>0.711</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J26" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0.445</v>
@@ -5056,37 +5123,37 @@
         <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
         <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="T26" t="n">
-        <v>45.5</v>
+        <v>45.7</v>
       </c>
       <c r="U26" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V26" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
         <v>5.1</v>
@@ -5098,16 +5165,16 @@
         <v>19.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.8</v>
+        <v>103</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5119,10 +5186,10 @@
         <v>4</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
@@ -5152,31 +5219,31 @@
         <v>15</v>
       </c>
       <c r="AS26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5211,58 +5278,58 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" t="n">
-        <v>0.364</v>
+        <v>0.372</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J27" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.457</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
         <v>15.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.332</v>
       </c>
       <c r="O27" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="P27" t="n">
         <v>29.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R27" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="S27" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="T27" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="U27" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V27" t="n">
         <v>16.5</v>
@@ -5277,7 +5344,7 @@
         <v>6.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA27" t="n">
         <v>24.8</v>
@@ -5286,7 +5353,7 @@
         <v>101.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.9</v>
+        <v>-2.6</v>
       </c>
       <c r="AD27" t="n">
         <v>28</v>
@@ -5295,7 +5362,7 @@
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
         <v>21</v>
@@ -5304,13 +5371,13 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5328,16 +5395,16 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5361,10 +5428,10 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5411,67 +5478,67 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>22.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
         <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
         <v>20.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.3</v>
+        <v>101.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5489,10 +5556,10 @@
         <v>12</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5504,10 +5571,10 @@
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>11</v>
@@ -5516,19 +5583,19 @@
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5537,7 +5604,7 @@
         <v>15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
         <v>17</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5575,112 +5642,112 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.674</v>
+        <v>0.667</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J29" t="n">
         <v>84.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L29" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.346</v>
       </c>
       <c r="O29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P29" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
         <v>42</v>
       </c>
       <c r="U29" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V29" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
         <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
         <v>21.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>106</v>
+        <v>105.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE29" t="n">
         <v>8</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>6</v>
       </c>
       <c r="AF29" t="n">
         <v>7</v>
       </c>
       <c r="AG29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
         <v>16</v>
@@ -5692,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
@@ -5701,19 +5768,19 @@
         <v>26</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" t="n">
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G30" t="n">
-        <v>0.348</v>
+        <v>0.356</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
@@ -5784,37 +5851,37 @@
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P30" t="n">
         <v>22.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.749</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
         <v>30.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X30" t="n">
         <v>5.9</v>
@@ -5823,19 +5890,19 @@
         <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA30" t="n">
         <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="AC30" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
@@ -5865,10 +5932,10 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5904,13 +5971,13 @@
         <v>5</v>
       </c>
       <c r="BA30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
         <v>24</v>
       </c>
       <c r="BC30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
@@ -5939,106 +6006,106 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.66</v>
+        <v>0.674</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.474</v>
+        <v>0.476</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M31" t="n">
         <v>15.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O31" t="n">
         <v>15.8</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R31" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U31" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6059,13 +6126,13 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
@@ -6074,25 +6141,25 @@
         <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX31" t="n">
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-28-2014-15</t>
+          <t>2015-01-28</t>
         </is>
       </c>
     </row>
